--- a/mine/data/Excel/Preference.xlsx
+++ b/mine/data/Excel/Preference.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Python\ExcelToJson\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\mine\data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822389DE-F2F4-430E-B43D-2BD1FBBAFD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96270768-3494-4AF4-8727-32A968E61D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3849" yWindow="1843" windowWidth="16457" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -58,43 +58,12 @@
     <t>Card Game</t>
   </si>
   <si>
-    <t>Unity / Game System</t>
-  </si>
-  <si>
-    <t>Turn-based combat framework with modular deck architecture and scalable gameplay systems.</t>
-  </si>
-  <si>
-    <t>Project_CardGame.html</t>
-  </si>
-  <si>
-    <t>../Raw/Img/project-cardgame.jpg</t>
-  </si>
-  <si>
-    <t>Cooking Simulator</t>
-  </si>
-  <si>
-    <t>Dice Experiment</t>
-  </si>
-  <si>
-    <t>SPA Demo</t>
-  </si>
-  <si>
-    <t>Cooking Prototype</t>
-  </si>
-  <si>
-    <t>../cook/index.html</t>
-  </si>
-  <si>
-    <t>../spa.html</t>
-  </si>
-  <si>
-    <t>../touzi.html</t>
-  </si>
-  <si>
-    <t>Project_CookGame.html</t>
-  </si>
-  <si>
-    <t>Restaurant simulation focused on AI customer behavior, cooking workflow and management mechanics.</t>
+    <t>Music</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Preference/Project_CardGame.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -419,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -460,61 +429,8 @@
       <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
